--- a/artfynd/A 12708-2025 artfynd.xlsx
+++ b/artfynd/A 12708-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>113337134</v>
       </c>
       <c r="B2" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,55 +777,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113337021</v>
+        <v>113406808</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581847</v>
+        <v>581417</v>
       </c>
       <c r="R3" t="n">
-        <v>6320893</v>
+        <v>6320565</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,12 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +868,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -901,55 +886,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113336998</v>
+        <v>116472836</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581806</v>
+        <v>581656</v>
       </c>
       <c r="R4" t="n">
-        <v>6320747</v>
+        <v>6320697</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -987,12 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +977,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1020,66 +995,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113336990</v>
+        <v>116453688</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Granshult 1:7, Sm</t>
+          <t>Bräkamossen, Bräkamossen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581786</v>
+        <v>581426</v>
       </c>
       <c r="R5" t="n">
-        <v>6320742</v>
+        <v>6320691</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1106,12 +1065,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,34 +1079,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113337140</v>
+        <v>113336990</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,7 +1127,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1195,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581820</v>
+        <v>581786</v>
       </c>
       <c r="R6" t="n">
-        <v>6320884</v>
+        <v>6320742</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1258,15 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113406532</v>
+        <v>113336998</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1241,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1314,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581362</v>
+        <v>581806</v>
       </c>
       <c r="R7" t="n">
-        <v>6320744</v>
+        <v>6320747</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1344,12 +1292,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,15 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113406627</v>
+        <v>113337021</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1355,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1433,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581305</v>
+        <v>581847</v>
       </c>
       <c r="R8" t="n">
-        <v>6320582</v>
+        <v>6320893</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1463,12 +1406,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,15 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113406360</v>
+        <v>113337140</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1469,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1552,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581719</v>
+        <v>581820</v>
       </c>
       <c r="R9" t="n">
-        <v>6320719</v>
+        <v>6320884</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1582,12 +1520,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,15 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113406509</v>
+        <v>113406355</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1583,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1671,10 +1604,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581381</v>
+        <v>581800</v>
       </c>
       <c r="R10" t="n">
-        <v>6320713</v>
+        <v>6320752</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1734,15 +1667,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116473019</v>
+        <v>113406360</v>
       </c>
       <c r="B11" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1769,7 +1697,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1790,13 +1718,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581413</v>
+        <v>581719</v>
       </c>
       <c r="R11" t="n">
-        <v>6320610</v>
+        <v>6320719</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1820,12 +1748,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,42 +1781,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113406585</v>
+        <v>113406366</v>
       </c>
       <c r="B12" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1909,10 +1832,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581371</v>
+        <v>581717</v>
       </c>
       <c r="R12" t="n">
-        <v>6320640</v>
+        <v>6320699</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1972,15 +1895,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113406699</v>
+        <v>113406498</v>
       </c>
       <c r="B13" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +1925,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2028,10 +1946,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581390</v>
+        <v>581428</v>
       </c>
       <c r="R13" t="n">
-        <v>6320580</v>
+        <v>6320682</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2091,15 +2009,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113406703</v>
+        <v>113406501</v>
       </c>
       <c r="B14" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2039,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2147,10 +2060,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581396</v>
+        <v>581392</v>
       </c>
       <c r="R14" t="n">
-        <v>6320584</v>
+        <v>6320705</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2210,15 +2123,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113406355</v>
+        <v>113406509</v>
       </c>
       <c r="B15" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2245,7 +2153,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2266,10 +2174,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581800</v>
+        <v>581381</v>
       </c>
       <c r="R15" t="n">
-        <v>6320752</v>
+        <v>6320713</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2329,15 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113406611</v>
+        <v>113406523</v>
       </c>
       <c r="B16" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2267,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2385,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581291</v>
+        <v>581366</v>
       </c>
       <c r="R16" t="n">
-        <v>6320617</v>
+        <v>6320707</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2448,15 +2351,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113406501</v>
+        <v>113406532</v>
       </c>
       <c r="B17" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2483,7 +2381,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2504,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581392</v>
+        <v>581362</v>
       </c>
       <c r="R17" t="n">
-        <v>6320705</v>
+        <v>6320744</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2567,15 +2465,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113406649</v>
+        <v>113406541</v>
       </c>
       <c r="B18" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2495,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2623,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581324</v>
+        <v>581342</v>
       </c>
       <c r="R18" t="n">
-        <v>6320559</v>
+        <v>6320739</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2686,15 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113406366</v>
+        <v>113406550</v>
       </c>
       <c r="B19" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2609,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2742,10 +2630,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581717</v>
+        <v>581315</v>
       </c>
       <c r="R19" t="n">
-        <v>6320699</v>
+        <v>6320715</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2805,15 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113406604</v>
+        <v>113406558</v>
       </c>
       <c r="B20" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2840,7 +2723,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2861,10 +2744,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581322</v>
+        <v>581324</v>
       </c>
       <c r="R20" t="n">
-        <v>6320613</v>
+        <v>6320682</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2924,15 +2807,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113406541</v>
+        <v>113406573</v>
       </c>
       <c r="B21" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2959,7 +2837,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2980,10 +2858,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581342</v>
+        <v>581335</v>
       </c>
       <c r="R21" t="n">
-        <v>6320739</v>
+        <v>6320648</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3043,51 +2921,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113406808</v>
+        <v>113406597</v>
       </c>
       <c r="B22" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3095,13 +2972,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581417</v>
+        <v>581355</v>
       </c>
       <c r="R22" t="n">
-        <v>6320565</v>
+        <v>6320627</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3139,6 +3016,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3157,42 +3035,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113406529</v>
+        <v>113406604</v>
       </c>
       <c r="B23" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3213,10 +3086,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581370</v>
+        <v>581322</v>
       </c>
       <c r="R23" t="n">
-        <v>6320727</v>
+        <v>6320613</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3276,15 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113406597</v>
+        <v>113406611</v>
       </c>
       <c r="B24" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3311,7 +3179,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3332,10 +3200,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581355</v>
+        <v>581291</v>
       </c>
       <c r="R24" t="n">
-        <v>6320627</v>
+        <v>6320617</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3395,15 +3263,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113406523</v>
+        <v>113406627</v>
       </c>
       <c r="B25" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3430,7 +3293,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3451,10 +3314,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581366</v>
+        <v>581305</v>
       </c>
       <c r="R25" t="n">
-        <v>6320707</v>
+        <v>6320582</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3514,15 +3377,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113406738</v>
+        <v>113406649</v>
       </c>
       <c r="B26" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3549,7 +3407,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3570,10 +3428,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581355</v>
+        <v>581324</v>
       </c>
       <c r="R26" t="n">
-        <v>6320562</v>
+        <v>6320559</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3633,15 +3491,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113406673</v>
+        <v>113406669</v>
       </c>
       <c r="B27" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3668,7 +3521,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3689,10 +3542,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581391</v>
+        <v>581345</v>
       </c>
       <c r="R27" t="n">
-        <v>6320619</v>
+        <v>6320584</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3752,15 +3605,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113406763</v>
+        <v>113406673</v>
       </c>
       <c r="B28" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3787,7 +3635,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3808,10 +3656,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581388</v>
+        <v>581391</v>
       </c>
       <c r="R28" t="n">
-        <v>6320495</v>
+        <v>6320619</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3871,15 +3719,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113406749</v>
+        <v>116473019</v>
       </c>
       <c r="B29" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3906,7 +3749,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3927,13 +3770,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581359</v>
+        <v>581413</v>
       </c>
       <c r="R29" t="n">
-        <v>6320536</v>
+        <v>6320610</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3957,12 +3800,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3990,15 +3833,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113406550</v>
+        <v>113406690</v>
       </c>
       <c r="B30" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4025,7 +3863,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4046,10 +3884,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581315</v>
+        <v>581424</v>
       </c>
       <c r="R30" t="n">
-        <v>6320715</v>
+        <v>6320587</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4109,15 +3947,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113406669</v>
+        <v>113406699</v>
       </c>
       <c r="B31" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4144,7 +3977,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4165,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581345</v>
+        <v>581390</v>
       </c>
       <c r="R31" t="n">
-        <v>6320584</v>
+        <v>6320580</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4228,15 +4061,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113406558</v>
+        <v>113406703</v>
       </c>
       <c r="B32" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4263,7 +4091,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4284,10 +4112,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581324</v>
+        <v>581396</v>
       </c>
       <c r="R32" t="n">
-        <v>6320682</v>
+        <v>6320584</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4350,12 +4178,7 @@
         <v>113406716</v>
       </c>
       <c r="B33" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4466,15 +4289,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113406573</v>
+        <v>113406738</v>
       </c>
       <c r="B34" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4501,7 +4319,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4522,10 +4340,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581335</v>
+        <v>581355</v>
       </c>
       <c r="R34" t="n">
-        <v>6320648</v>
+        <v>6320562</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4585,15 +4403,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113406498</v>
+        <v>113406749</v>
       </c>
       <c r="B35" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4620,7 +4433,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4641,10 +4454,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581428</v>
+        <v>581359</v>
       </c>
       <c r="R35" t="n">
-        <v>6320682</v>
+        <v>6320536</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4704,15 +4517,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>116473035</v>
+        <v>113406763</v>
       </c>
       <c r="B36" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4739,7 +4547,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4760,13 +4568,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581344</v>
+        <v>581388</v>
       </c>
       <c r="R36" t="n">
-        <v>6320709</v>
+        <v>6320495</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4790,12 +4598,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4826,12 +4634,7 @@
         <v>116452742</v>
       </c>
       <c r="B37" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4868,7 +4671,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bräkamossen (Bräkamossen), Sm</t>
+          <t>Bräkamossen, Bräkamossen, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
@@ -4934,58 +4737,64 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>116453688</v>
+        <v>116473035</v>
       </c>
       <c r="B38" t="n">
-        <v>57426</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bräkamossen (Bräkamossen), Sm</t>
+          <t>Granshult 1:7, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581426</v>
+        <v>581344</v>
       </c>
       <c r="R38" t="n">
-        <v>6320691</v>
+        <v>6320709</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5023,18 +4832,19 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5044,12 +4854,7 @@
         <v>116473071</v>
       </c>
       <c r="B39" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5157,6 +4962,234 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>113406529</v>
+      </c>
+      <c r="B40" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Granshult 1:7, Sm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>581370</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6320727</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>113406585</v>
+      </c>
+      <c r="B41" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Granshult 1:7, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>581371</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6320640</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12708-2025 artfynd.xlsx
+++ b/artfynd/A 12708-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337134</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406808</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116472836</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116453688</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1208,6 +1233,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113336990</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1322,6 +1352,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113336998</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1436,6 +1471,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337021</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1550,6 +1590,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337140</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1664,6 +1709,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406355</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1778,6 +1828,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406360</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1892,6 +1947,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406366</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2006,6 +2066,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406498</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2120,6 +2185,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406501</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2234,6 +2304,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406509</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2348,6 +2423,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406523</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2462,6 +2542,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406532</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2576,6 +2661,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406541</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2690,6 +2780,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406550</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2804,6 +2899,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406558</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2918,6 +3018,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406573</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3032,6 +3137,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406597</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3146,6 +3256,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406604</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3260,6 +3375,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406611</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3374,6 +3494,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406627</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3488,6 +3613,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406649</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3602,6 +3732,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406669</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3716,6 +3851,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406673</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3830,6 +3970,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116473019</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3944,6 +4089,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406690</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4058,6 +4208,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406699</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4172,6 +4327,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406703</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4286,6 +4446,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406716</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4400,6 +4565,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406738</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4514,6 +4684,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406749</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4628,6 +4803,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406763</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4734,6 +4914,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116452742</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4848,6 +5033,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116473035</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4962,6 +5152,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116473071</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5076,6 +5271,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406529</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5190,8 +5390,55 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406585</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>